--- a/data/trans_dic/IMC_inf_MED_R3-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_MED_R3-Clase-trans_dic.xlsx
@@ -532,7 +532,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido (tasa de respuesta: 71,23%)</t>
+          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido (tasa de respuesta: 79,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -632,31 +632,31 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0.2179445029921938</v>
+        <v>0.1807631831154169</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0.1935426857007771</v>
+        <v>0.1648221900077274</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.09666615979837974</v>
+        <v>0.09222367574974095</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.2234495124374375</v>
+        <v>0.2118208762012205</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.1495397773366751</v>
+        <v>0.1332856190281185</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0.1049150594486263</v>
+        <v>0.102680748143465</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0.220901240419376</v>
+        <v>0.1970372549001246</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>0.1737025224448562</v>
+        <v>0.1508615495216</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>0.1001847543884441</v>
+        <v>0.09661902240265521</v>
       </c>
     </row>
     <row r="5">
@@ -667,31 +667,31 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.1368535301956118</v>
+        <v>0.1084565238063475</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.1257706348962283</v>
+        <v>0.1040572549031738</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.04193362774548676</v>
+        <v>0.04138379801810717</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.1511004388910385</v>
+        <v>0.1479750826385922</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.08557274615100688</v>
+        <v>0.08115059974647701</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>0.04164228146453473</v>
+        <v>0.04350124745005089</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>0.16517993308157</v>
+        <v>0.146917312123732</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0.1260983684615845</v>
+        <v>0.1052489288345762</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>0.05652926442093679</v>
+        <v>0.05358413285378695</v>
       </c>
     </row>
     <row r="6">
@@ -702,31 +702,31 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.3132846658238065</v>
+        <v>0.2620394629233457</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.2772350859211987</v>
+        <v>0.237103632574856</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.1770214391538174</v>
+        <v>0.1742732040567143</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.3247031324986395</v>
+        <v>0.3086599014147073</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.2566276657187054</v>
+        <v>0.2269096318096814</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0.2367517391009363</v>
+        <v>0.2209070341042098</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.2839314080592364</v>
+        <v>0.2564602520745066</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.2368418201736078</v>
+        <v>0.2023751709133279</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>0.1667077857833121</v>
+        <v>0.1579703110603378</v>
       </c>
     </row>
     <row r="7">
@@ -741,31 +741,31 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.2621230979153835</v>
+        <v>0.234085820616258</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.1489505062419707</v>
+        <v>0.1456988502669421</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.1687255768262762</v>
+        <v>0.1661710145117522</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.1894033430051109</v>
+        <v>0.1720960917390693</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.06839138560369563</v>
+        <v>0.08238392126666584</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0.08657310316396408</v>
+        <v>0.08093628841346513</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0.2253023649226604</v>
+        <v>0.2036213705325387</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>0.1120280594920845</v>
+        <v>0.1161475472666146</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>0.1285093319931687</v>
+        <v>0.1233364819584688</v>
       </c>
     </row>
     <row r="8">
@@ -776,31 +776,31 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0.1735657381494902</v>
+        <v>0.1602659861339404</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0.09584062740568858</v>
+        <v>0.08961196604266979</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.0860973940462334</v>
+        <v>0.07712116897213839</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.1216931525203855</v>
+        <v>0.1064535645812061</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0332160264209529</v>
+        <v>0.04397814717924489</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>0.03564913305339732</v>
+        <v>0.03268481374199971</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>0.1729542293217687</v>
+        <v>0.1579996178930277</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>0.07763271652953001</v>
+        <v>0.0802192937241936</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>0.08037999904561502</v>
+        <v>0.07392980561045333</v>
       </c>
     </row>
     <row r="9">
@@ -811,31 +811,31 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.3455986163287468</v>
+        <v>0.3128820712657818</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.2198931290975886</v>
+        <v>0.2142204263084874</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.2873889728646655</v>
+        <v>0.2811496967577831</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.281488771258194</v>
+        <v>0.2521412405042381</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.1284815901505456</v>
+        <v>0.1393499673112803</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0.1800804247229498</v>
+        <v>0.1670669936050407</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>0.2858724410918863</v>
+        <v>0.2650806802742173</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>0.1548178453029425</v>
+        <v>0.159234678774876</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>0.2042176840136879</v>
+        <v>0.1893864955423283</v>
       </c>
     </row>
     <row r="10">
@@ -850,31 +850,31 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.3118627533986425</v>
+        <v>0.2817590936869661</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0.2753030032398064</v>
+        <v>0.2637757123016692</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.2494111935852272</v>
+        <v>0.2356929228245666</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.2036011594003728</v>
+        <v>0.1862314719444784</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.1025289851505094</v>
+        <v>0.1110926102059442</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0.1169564123209145</v>
+        <v>0.1281830106374574</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.2574049180740419</v>
+        <v>0.2325885565132677</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0.1985077806334933</v>
+        <v>0.1950691760338673</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>0.1989242997137595</v>
+        <v>0.1927256411674446</v>
       </c>
     </row>
     <row r="11">
@@ -885,31 +885,31 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0.2218697165448557</v>
+        <v>0.1912135242966658</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0.1889986431303466</v>
+        <v>0.1769006079123047</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.1275599099563548</v>
+        <v>0.1268157394918108</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.1262611901400157</v>
+        <v>0.1219732479498272</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.04263238316819332</v>
+        <v>0.05791888662962349</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0.03398767779119641</v>
+        <v>0.04522965852690099</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.1925462309236269</v>
+        <v>0.1770929733952184</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0.1384429311288386</v>
+        <v>0.141285430476938</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>0.1156637623225022</v>
+        <v>0.1153150984715334</v>
       </c>
     </row>
     <row r="12">
@@ -920,31 +920,31 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0.4150793136719574</v>
+        <v>0.3722862068787268</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0.388860465686619</v>
+        <v>0.3494582966109764</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.391560943324182</v>
+        <v>0.3965353236427965</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.3033086245161741</v>
+        <v>0.2642659753689749</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.1977537963984085</v>
+        <v>0.1936400484717098</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.2939102260065496</v>
+        <v>0.3009107021091331</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.3243125223681464</v>
+        <v>0.300484478368391</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.2644011340342674</v>
+        <v>0.258620262371637</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>0.3139177217921547</v>
+        <v>0.2934391767823863</v>
       </c>
     </row>
     <row r="13">
@@ -959,31 +959,31 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.288832753011954</v>
+        <v>0.269512183944968</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0.2117084400358848</v>
+        <v>0.2053890418566688</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.2114363217392745</v>
+        <v>0.199489612046059</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.2330034155063735</v>
+        <v>0.2197191641661296</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.1564263044890468</v>
+        <v>0.1376356353991957</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>0.1073515736203532</v>
+        <v>0.1044953060025604</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.2632239230934917</v>
+        <v>0.246285799814924</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.1835075450692938</v>
+        <v>0.1716692100711909</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>0.1610817151658112</v>
+        <v>0.1542724380109269</v>
       </c>
     </row>
     <row r="14">
@@ -994,31 +994,31 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0.2305848689190227</v>
+        <v>0.2196953919803714</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>0.1625974105983069</v>
+        <v>0.1573153418491808</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.1373524818121045</v>
+        <v>0.1303647460964132</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.1706893972596205</v>
+        <v>0.1721186285759744</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.1122677960725125</v>
+        <v>0.1018681422038791</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>0.06421977594083098</v>
+        <v>0.06183104412291535</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0.2230408300817361</v>
+        <v>0.2107478580226003</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0.1476306473114343</v>
+        <v>0.1428515068493872</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>0.1084854315679945</v>
+        <v>0.110577907085279</v>
       </c>
     </row>
     <row r="15">
@@ -1029,31 +1029,31 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0.3524582028493574</v>
+        <v>0.32930501509667</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0.2757557741585625</v>
+        <v>0.262583199647571</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.3098079589656708</v>
+        <v>0.2920623196114355</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.3024273895379906</v>
+        <v>0.2766611661176092</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.2128466313853609</v>
+        <v>0.184518591002113</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>0.1732614029283338</v>
+        <v>0.1711014332410795</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.3111823461615225</v>
+        <v>0.2846845071639049</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>0.2241408439924501</v>
+        <v>0.209257513726245</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.2138261409371184</v>
+        <v>0.2080224123733598</v>
       </c>
     </row>
     <row r="16">
@@ -1068,31 +1068,31 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.2993130855931196</v>
+        <v>0.2892265171204015</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>0.2262189308312182</v>
+        <v>0.1996882834735372</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.2713765542265071</v>
+        <v>0.2558733355679087</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.2218046949306867</v>
+        <v>0.2258881950024376</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.1496985113309979</v>
+        <v>0.1327149118007199</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>0.2149924117468429</v>
+        <v>0.2273046233735251</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.2587150676838008</v>
+        <v>0.2567377540033388</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0.1886709975480347</v>
+        <v>0.1666828884986559</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0.2493212559165866</v>
+        <v>0.2445072180762874</v>
       </c>
     </row>
     <row r="17">
@@ -1103,31 +1103,31 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0.2293119089207572</v>
+        <v>0.2234251131941634</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0.1583425777218756</v>
+        <v>0.1461161596829173</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.1823924001252596</v>
+        <v>0.1640910458927803</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.1662613150070337</v>
+        <v>0.1673088479970622</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.09905641812577595</v>
+        <v>0.08914352417634014</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>0.1167992413905655</v>
+        <v>0.1318350257237182</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>0.209574975683876</v>
+        <v>0.2134992299690018</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0.1442620783594991</v>
+        <v>0.1295402620595634</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>0.178906191009674</v>
+        <v>0.1758896597406542</v>
       </c>
     </row>
     <row r="18">
@@ -1138,31 +1138,31 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.3799963999626317</v>
+        <v>0.3598358839675305</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>0.3034394050437326</v>
+        <v>0.2659039579458326</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.3754749285313597</v>
+        <v>0.372413882514494</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.2954958530774942</v>
+        <v>0.2886569968521557</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.214668480818741</v>
+        <v>0.1856587197786868</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>0.3522082911957125</v>
+        <v>0.3582750492480918</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>0.3096782822864353</v>
+        <v>0.3047064691356323</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>0.2361669867487948</v>
+        <v>0.2102340945521037</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>0.3393003346094844</v>
+        <v>0.3295311644673202</v>
       </c>
     </row>
     <row r="19">
@@ -1177,28 +1177,28 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>0.3112176103058159</v>
+        <v>0.2787339409584163</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>0.232069245166383</v>
+        <v>0.2338471589112371</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>0.1775524239617922</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.2839244973561185</v>
+        <v>0.29912851672487</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.1671191472339087</v>
+        <v>0.150358239705164</v>
       </c>
       <c r="H19" s="5" t="n">
         <v>0.08217800133767517</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>0.299449655213627</v>
+        <v>0.287248564003138</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>0.2018604432533457</v>
+        <v>0.1958815757051213</v>
       </c>
       <c r="K19" s="5" t="n">
         <v>0.1352070380563853</v>
@@ -1212,28 +1212,28 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>0.2183083569556674</v>
+        <v>0.1862180805601615</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>0.1401914384996414</v>
+        <v>0.1558118492171937</v>
       </c>
       <c r="E20" s="5" t="n">
         <v>0.08070416057088413</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.1838532673474886</v>
+        <v>0.1915089365076081</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.08675342548251153</v>
+        <v>0.08138496705450668</v>
       </c>
       <c r="H20" s="5" t="n">
         <v>0.01839375652029554</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>0.2292927307352631</v>
+        <v>0.2211282582368756</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0.141552029240342</v>
+        <v>0.1320125720186946</v>
       </c>
       <c r="K20" s="5" t="n">
         <v>0.06912627924604717</v>
@@ -1247,28 +1247,28 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0.4214047530778381</v>
+        <v>0.3793678708188071</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>0.3496419283609253</v>
+        <v>0.3271425931932774</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>0.3283406750235721</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.4043774760820137</v>
+        <v>0.4225770375594928</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.2904612117073092</v>
+        <v>0.2589185918626215</v>
       </c>
       <c r="H21" s="5" t="n">
         <v>0.2268582867625339</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>0.3888247968658628</v>
+        <v>0.3646353622991118</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>0.2799669041975941</v>
+        <v>0.2625858487696707</v>
       </c>
       <c r="K21" s="5" t="n">
         <v>0.2310224020039825</v>
@@ -1286,31 +1286,31 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.2842758216275966</v>
+        <v>0.2607955691213584</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>0.2112465556139622</v>
+        <v>0.1984983637635648</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.1948085260965677</v>
+        <v>0.1869568303792374</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.2233071532372957</v>
+        <v>0.2156045438440373</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.1365186101494964</v>
+        <v>0.1262734130663447</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>0.1169186301903563</v>
+        <v>0.1187350077033143</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0.2542672437833857</v>
+        <v>0.2387168079875909</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>0.1754372607237008</v>
+        <v>0.1641055216696947</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>0.1601025912962567</v>
+        <v>0.1565117931648985</v>
       </c>
     </row>
     <row r="23">
@@ -1321,31 +1321,31 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>0.2531854981751872</v>
+        <v>0.2341246810968234</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>0.1814177924395368</v>
+        <v>0.1730794203173929</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0.1604085492871668</v>
+        <v>0.1531667703267386</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.1920973944126468</v>
+        <v>0.1874472850717156</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.1118368538296248</v>
+        <v>0.1061853960882611</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>0.08687525395291937</v>
+        <v>0.09031329681590375</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>0.2337139722453175</v>
+        <v>0.2184277538125873</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>0.1568826406308443</v>
+        <v>0.1453084892233821</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>0.1343305021466333</v>
+        <v>0.1318583251594932</v>
       </c>
     </row>
     <row r="24">
@@ -1356,31 +1356,31 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>0.3208814973580582</v>
+        <v>0.2900331570426288</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>0.2417273581589527</v>
+        <v>0.2267875022601232</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0.2378314114666072</v>
+        <v>0.2305415822540822</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.2546669378437136</v>
+        <v>0.2430602353152329</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.1625670908932944</v>
+        <v>0.1508089432480762</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>0.1533162025133784</v>
+        <v>0.15353739450664</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>0.2778339588419336</v>
+        <v>0.2584719750620495</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>0.1964351298779729</v>
+        <v>0.1805624777594108</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>0.188781206125937</v>
+        <v>0.1830115374881159</v>
       </c>
     </row>
     <row r="25">
@@ -1433,7 +1433,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido (tasa de respuesta: 71,23%)</t>
+          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido (tasa de respuesta: 79,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1536,25 +1536,25 @@
         <v>18</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>8</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>6</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K4" s="6" t="n">
         <v>14</v>
@@ -1571,25 +1571,25 @@
         <v>12529</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>12537</v>
+        <v>13113</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>5158</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>14904</v>
+        <v>16162</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>7954</v>
+        <v>8423</v>
       </c>
       <c r="H5" s="6" t="n">
         <v>4164</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>27433</v>
+        <v>28690</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>20491</v>
+        <v>21535</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>9322</v>
@@ -1603,31 +1603,31 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>7867</v>
+        <v>7517</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>8147</v>
+        <v>8278</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>2238</v>
+        <v>2315</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>10078</v>
+        <v>11290</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>4552</v>
+        <v>5128</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>1653</v>
+        <v>1764</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>20513</v>
+        <v>21392</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>14875</v>
+        <v>15024</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>5260</v>
+        <v>5170</v>
       </c>
     </row>
     <row r="7">
@@ -1638,31 +1638,31 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>18009</v>
+        <v>18162</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>17958</v>
+        <v>18863</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>9446</v>
+        <v>9747</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>21658</v>
+        <v>23550</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>13650</v>
+        <v>14339</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>9397</v>
+        <v>8959</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>35260</v>
+        <v>37343</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>27939</v>
+        <v>28888</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>15512</v>
+        <v>15242</v>
       </c>
     </row>
     <row r="8">
@@ -1677,10 +1677,10 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>10</v>
@@ -1689,16 +1689,16 @@
         <v>19</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>7</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K8" s="6" t="n">
         <v>17</v>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>18003</v>
+        <v>18781</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>12298</v>
+        <v>13775</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>7038</v>
@@ -1724,16 +1724,16 @@
         <v>13343</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>4778</v>
+        <v>6817</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>3463</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>31346</v>
+        <v>32123</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>17076</v>
+        <v>20592</v>
       </c>
       <c r="K9" s="6" t="n">
         <v>10501</v>
@@ -1747,31 +1747,31 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>11921</v>
+        <v>12858</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>7913</v>
+        <v>8472</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>3591</v>
+        <v>3266</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>8573</v>
+        <v>8253</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>2321</v>
+        <v>3639</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>1426</v>
+        <v>1398</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>24063</v>
+        <v>24926</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>11834</v>
+        <v>14222</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>6568</v>
+        <v>6294</v>
       </c>
     </row>
     <row r="11">
@@ -1782,31 +1782,31 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>23736</v>
+        <v>25103</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>18156</v>
+        <v>20253</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>11988</v>
+        <v>11908</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>19830</v>
+        <v>19549</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>8976</v>
+        <v>11531</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>7204</v>
+        <v>7148</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>39773</v>
+        <v>41819</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>23599</v>
+        <v>28231</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>16687</v>
+        <v>16125</v>
       </c>
     </row>
     <row r="12">
@@ -1824,28 +1824,28 @@
         <v>26</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>11</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -1859,28 +1859,28 @@
         <v>19063</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>15741</v>
+        <v>17017</v>
       </c>
       <c r="E13" s="6" t="n">
         <v>6911</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>12597</v>
+        <v>13364</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>4691</v>
+        <v>5864</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>1996</v>
+        <v>2502</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>31659</v>
+        <v>32427</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>20432</v>
+        <v>22881</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>8908</v>
+        <v>9414</v>
       </c>
     </row>
     <row r="14">
@@ -1891,31 +1891,31 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>13562</v>
+        <v>12937</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>10807</v>
+        <v>11413</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>3535</v>
+        <v>3719</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>7812</v>
+        <v>8753</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>1950</v>
+        <v>3057</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>580</v>
+        <v>883</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>23682</v>
+        <v>24690</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>14250</v>
+        <v>16573</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>5179</v>
+        <v>5633</v>
       </c>
     </row>
     <row r="15">
@@ -1926,31 +1926,31 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>25372</v>
+        <v>25187</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>22234</v>
+        <v>22545</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>10851</v>
+        <v>11628</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>18765</v>
+        <v>18964</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>9047</v>
+        <v>10221</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>5016</v>
+        <v>5874</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>39888</v>
+        <v>41893</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>27214</v>
+        <v>30336</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>14057</v>
+        <v>14333</v>
       </c>
     </row>
     <row r="16">
@@ -1965,28 +1965,28 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>26</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>15</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K16" s="6" t="n">
         <v>41</v>
@@ -2000,28 +2000,28 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>44902</v>
+        <v>50598</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>30635</v>
+        <v>37308</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>16888</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>30695</v>
+        <v>36063</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>23572</v>
+        <v>24771</v>
       </c>
       <c r="H17" s="6" t="n">
         <v>8036</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>75597</v>
+        <v>86661</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>54207</v>
+        <v>62079</v>
       </c>
       <c r="K17" s="6" t="n">
         <v>24924</v>
@@ -2035,31 +2035,31 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>35846</v>
+        <v>41245</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>23529</v>
+        <v>28576</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>10971</v>
+        <v>11036</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>22486</v>
+        <v>28250</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>16918</v>
+        <v>18333</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>4807</v>
+        <v>4755</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>64056</v>
+        <v>74156</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>43609</v>
+        <v>51658</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>16786</v>
+        <v>17865</v>
       </c>
     </row>
     <row r="19">
@@ -2070,31 +2070,31 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>54793</v>
+        <v>61823</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>39904</v>
+        <v>47697</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>24746</v>
+        <v>24725</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>39841</v>
+        <v>45409</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>32074</v>
+        <v>33208</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>12970</v>
+        <v>13158</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>89370</v>
+        <v>100172</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>66210</v>
+        <v>75671</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>33085</v>
+        <v>33608</v>
       </c>
     </row>
     <row r="20">
@@ -2109,31 +2109,31 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="F20" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="D20" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>35</v>
-      </c>
       <c r="G20" s="6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21">
@@ -2144,31 +2144,31 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>29530</v>
+        <v>35699</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>22867</v>
+        <v>24697</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>14429</v>
+        <v>14884</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>24069</v>
+        <v>29363</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>14579</v>
+        <v>15949</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>7344</v>
+        <v>8736</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>53599</v>
+        <v>65062</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>37446</v>
+        <v>40646</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>21773</v>
+        <v>23620</v>
       </c>
     </row>
     <row r="22">
@@ -2179,31 +2179,31 @@
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>22624</v>
+        <v>27577</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>16006</v>
+        <v>18071</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>9697</v>
+        <v>9545</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>18042</v>
+        <v>21748</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>9647</v>
+        <v>10713</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>3990</v>
+        <v>5067</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>43418</v>
+        <v>54105</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>28632</v>
+        <v>31589</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>15624</v>
+        <v>16991</v>
       </c>
     </row>
     <row r="23">
@@ -2214,31 +2214,31 @@
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>37490</v>
+        <v>44415</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>30673</v>
+        <v>32886</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>19963</v>
+        <v>21663</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>32066</v>
+        <v>37522</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>20906</v>
+        <v>22311</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>12031</v>
+        <v>13770</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>64157</v>
+        <v>77218</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>46873</v>
+        <v>51266</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>29630</v>
+        <v>31833</v>
       </c>
     </row>
     <row r="24">
@@ -2253,16 +2253,16 @@
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E24" s="6" t="n">
         <v>7</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>10</v>
@@ -2271,10 +2271,10 @@
         <v>3</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K24" s="6" t="n">
         <v>10</v>
@@ -2288,16 +2288,16 @@
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>16823</v>
+        <v>17496</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>11674</v>
+        <v>13633</v>
       </c>
       <c r="E25" s="6" t="n">
         <v>6044</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>11634</v>
+        <v>13457</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>7310</v>
@@ -2306,10 +2306,10 @@
         <v>2234</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>28457</v>
+        <v>30954</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>18985</v>
+        <v>20943</v>
       </c>
       <c r="K25" s="6" t="n">
         <v>8278</v>
@@ -2323,28 +2323,28 @@
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>11801</v>
+        <v>11689</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>7052</v>
+        <v>9084</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>2747</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>7533</v>
+        <v>8616</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>3795</v>
+        <v>3957</v>
       </c>
       <c r="H26" s="6" t="n">
         <v>500</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>21790</v>
+        <v>23829</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>13313</v>
+        <v>14115</v>
       </c>
       <c r="K26" s="6" t="n">
         <v>4232</v>
@@ -2358,28 +2358,28 @@
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>22779</v>
+        <v>23813</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>17589</v>
+        <v>19072</v>
       </c>
       <c r="E27" s="6" t="n">
         <v>11177</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>16569</v>
+        <v>19011</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>12706</v>
+        <v>12588</v>
       </c>
       <c r="H27" s="6" t="n">
         <v>6166</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>36950</v>
+        <v>39293</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>26331</v>
+        <v>28075</v>
       </c>
       <c r="K27" s="6" t="n">
         <v>14143</v>
@@ -2397,31 +2397,31 @@
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>355</v>
+        <v>391</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>249</v>
+        <v>278</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="29">
@@ -2432,31 +2432,31 @@
         </is>
       </c>
       <c r="C29" s="6" t="n">
-        <v>140850</v>
+        <v>154165</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>105754</v>
+        <v>119543</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>56468</v>
+        <v>56923</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>107241</v>
+        <v>121752</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>62883</v>
+        <v>69133</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>27237</v>
+        <v>29135</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>248091</v>
+        <v>275917</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>168637</v>
+        <v>188677</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>83705</v>
+        <v>86059</v>
       </c>
     </row>
     <row r="30">
@@ -2467,31 +2467,31 @@
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>125445</v>
+        <v>138399</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>90821</v>
+        <v>104235</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>46497</v>
+        <v>46635</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>92253</v>
+        <v>105852</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>51515</v>
+        <v>58135</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>20238</v>
+        <v>22161</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>228037</v>
+        <v>252467</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>150802</v>
+        <v>167065</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>70231</v>
+        <v>72503</v>
       </c>
     </row>
     <row r="31">
@@ -2502,31 +2502,31 @@
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>158987</v>
+        <v>171449</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>121013</v>
+        <v>136580</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>68939</v>
+        <v>70194</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>122301</v>
+        <v>137256</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>74882</v>
+        <v>82566</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>35716</v>
+        <v>37675</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>271085</v>
+        <v>298751</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>188822</v>
+        <v>207598</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>98699</v>
+        <v>100630</v>
       </c>
     </row>
     <row r="32">
